--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1819,8 +1929,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -1839,624 +1953,507 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">님타령 — 민요채보-1/님타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">님타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="O3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="Q3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="15"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="15"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="16"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="Q9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="15"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="15"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -255,11 +255,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -6405,10 +6401,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s=""/>
-      <c r="B1" s="">
-        <v>0</v>
-      </c>
+      <c r="A1" s="0"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -706,12 +706,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -741,12 +741,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -964,12 +964,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -999,12 +999,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1231,13 +1231,13 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―㴌汰</t>
+          <t xml:space="preserve">汰|–㴌汰</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―㴌汰</t>
+–㴌汰</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1393,13 +1393,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1468,13 +1468,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―㴌</t>
+          <t xml:space="preserve">–|–㴌</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―㴌</t>
+          <t xml:space="preserve">–
+–㴌</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1547,13 +1547,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢|―</t>
+          <t xml:space="preserve">汰潢|–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1701,13 +1701,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1772,13 +1772,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I43" s="2"/>
@@ -2399,13 +2399,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―㴌汰</t>
+          <t xml:space="preserve">–|–㴌汰</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―㴌汰</t>
+          <t xml:space="preserve">–
+–㴌汰</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2478,13 +2478,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢|―</t>
+          <t xml:space="preserve">汰潢|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -2703,13 +2703,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -3252,13 +3252,13 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑‹</t>
+          <t xml:space="preserve">–姑‹</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑‹</t>
+          <t xml:space="preserve">–姑‹</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3564,13 +3564,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4553,12 +4553,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4589,13 +4589,13 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4823,13 +4823,13 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―</t>
+          <t xml:space="preserve">㴌|–</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I113" s="2"/>
@@ -4898,13 +4898,13 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢|―</t>
+          <t xml:space="preserve">汰潢|–</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I117" s="2"/>
@@ -5092,12 +5092,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I119" s="2"/>
@@ -5127,13 +5127,13 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I120" s="2"/>
@@ -5277,13 +5277,13 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I131" s="2"/>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌汰</t>
+          <t xml:space="preserve">–|㴌汰</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
@@ -5698,12 +5698,12 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I135" s="2"/>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南林</t>
+          <t xml:space="preserve">–|南林</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
@@ -5808,13 +5808,13 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I138" s="3"/>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I143" s="2"/>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南林</t>
+          <t xml:space="preserve">–|南林</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
@@ -6317,12 +6317,12 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -6435,7 +6435,7 @@
       <c r="B3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="11"/>
@@ -6453,7 +6453,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -6496,8 +6496,8 @@
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―㴌汰</t>
+          <t xml:space="preserve">–
+–㴌汰</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -6508,7 +6508,7 @@
       <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="Q3" s="8" t="inlineStr">
@@ -6650,7 +6650,7 @@
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -6705,7 +6705,7 @@
       <c r="N5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
@@ -6727,7 +6727,7 @@
       <c r="R5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―㴌汰</t>
+–㴌汰</t>
         </is>
       </c>
       <c r="S5" s="12" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="T6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U6" s="10"/>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="T7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U7" s="8"/>
@@ -6946,7 +6946,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O8" s="9"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="T8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="9"/>
@@ -7042,7 +7042,7 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -7075,7 +7075,7 @@
       <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -7104,7 +7104,7 @@
       <c r="R9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="S9" s="9" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="T9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U9" s="9"/>
@@ -7135,7 +7135,7 @@
       <c r="E10" s="16"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="10"/>
@@ -7147,7 +7147,7 @@
       <c r="I10" s="13"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -7172,7 +7172,7 @@
       <c r="Q10" s="10"/>
       <c r="R10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S10" s="10"/>
@@ -7206,7 +7206,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -7241,7 +7241,7 @@
       <c r="N11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr">
@@ -7261,8 +7261,8 @@
       </c>
       <c r="R11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―㴌</t>
+          <t xml:space="preserve">–
+–㴌</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
@@ -7292,7 +7292,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="9"/>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q12" s="9"/>
@@ -7369,14 +7369,14 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
@@ -7445,7 +7445,7 @@
       <c r="R13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="S13" s="9" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="10"/>
@@ -7502,7 +7502,7 @@
       <c r="K14" s="10"/>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑‹</t>
+          <t xml:space="preserve">–姑‹</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="10"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U14" s="10"/>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U15" s="8"/>
@@ -7648,13 +7648,13 @@
       <c r="C16" s="9"/>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G16" s="9"/>
@@ -7672,7 +7672,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -7702,13 +7702,13 @@
       </c>
       <c r="R16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S16" s="9"/>
       <c r="T16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U16" s="9"/>
@@ -7717,22 +7717,22 @@
       <c r="A17" s="0"/>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="G17" s="9"/>
@@ -7752,7 +7752,7 @@
       <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -7784,14 +7784,14 @@
       </c>
       <c r="R17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="S17" s="9"/>
       <c r="T17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -7823,7 +7823,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6405,135 +6452,135 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">님타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南林</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가를</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">임그</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하늘</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못오</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">물이</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –㴌汰</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –潢</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앞산</t>
         </is>
       </c>
-      <c r="R3" s="18" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세월</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">장을</t>
         </is>
@@ -6541,98 +6588,98 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -6640,107 +6687,107 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 ⁚</t>
         </is>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰汰
 汰</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이마</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △㴌</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">래무</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △㴌</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">세월</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △㴌</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어어</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">까지</t>
         </is>
       </c>
-      <c r="R5" s="18" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –㴌汰</t>
         </is>
       </c>
-      <c r="S5" s="12" t="inlineStr">
+      <c r="S5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라아</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U5" s="9" t="inlineStr">
+      <c r="U5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6748,535 +6795,535 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">엇이</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U6" s="10"/>
+      <c r="U6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 汰</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="24"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">높다</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">밉기</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못오</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢南</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못오</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U7" s="8"/>
+      <c r="U7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="26"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△林</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="S8" s="9" t="inlineStr">
+      <c r="S8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="9"/>
+      <c r="U8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="26"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="26"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 湳</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">여도</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 南</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하구나</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="O9" s="26"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 ·</t>
         </is>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
+      <c r="Q9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">덜</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="S9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U9" s="9"/>
+      <c r="U9" s="26"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="29"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="27"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="30"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="27"/>
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="27"/>
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="Q10" s="27"/>
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S10" s="10"/>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="S10" s="27"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U10" s="10"/>
+      <c r="U10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 汰</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이히</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">땅아</t>
         </is>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">해와</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –潢</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">산산</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다시</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –㴌</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가신</t>
         </is>
@@ -7284,82 +7331,82 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="26"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="26"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="J12" s="23"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="Q12" s="26"/>
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="S12" s="9" t="inlineStr">
+      <c r="S12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U12" s="9" t="inlineStr">
+      <c r="U12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -7367,98 +7414,98 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="26"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">히아</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 㴌</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="J13" s="23"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은다</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">높아</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">온다</t>
         </is>
       </c>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="S13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="U13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7466,336 +7513,336 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">엇이</t>
         </is>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="J14" s="23"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑‹</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="T14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 ⁚</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이이</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깊다</t>
         </is>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">바뀌</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 㴌</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못오</t>
         </is>
       </c>
-      <c r="P15" s="18" t="inlineStr">
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">철하</t>
         </is>
       </c>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="R15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="S15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아아</t>
         </is>
       </c>
-      <c r="T15" s="17" t="inlineStr">
+      <c r="T15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U15" s="8"/>
+      <c r="U15" s="24"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="26"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="26"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="26"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△林</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="J16" s="23"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O16" s="9" t="inlineStr">
+      <c r="O16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q16" s="9" t="inlineStr">
+      <c r="Q16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">던</t>
         </is>
       </c>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="R16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S16" s="9"/>
-      <c r="T16" s="17" t="inlineStr">
+      <c r="S16" s="26"/>
+      <c r="T16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U16" s="9"/>
+      <c r="U16" s="26"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="26"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="26"/>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="G17" s="26"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
 姑</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">여도</t>
         </is>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="J17" s="23"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 △㴌</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나아</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 ·</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
+      <c r="Q17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="R17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="S17" s="9"/>
-      <c r="T17" s="17" t="inlineStr">
+      <c r="S17" s="26"/>
+      <c r="T17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="U17" s="9" t="inlineStr">
+      <c r="U17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7803,67 +7850,67 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="C18" s="30"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="30"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="27"/>
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="O18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="Q18" s="27"/>
+      <c r="R18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S18" s="10"/>
-      <c r="T18" s="17" t="inlineStr">
+      <c r="S18" s="27"/>
+      <c r="T18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢△</t>
         </is>
       </c>
-      <c r="U18" s="10" t="inlineStr">
+      <c r="U18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -6425,32 +6425,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       <c r="C7" s="24"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="24"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="U7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="26"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="U8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="26"/>
@@ -7133,14 +7133,14 @@
       <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="O9" s="26"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-·</t>
+–</t>
         </is>
       </c>
       <c r="Q9" s="25" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="U9" s="26"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -7329,11 +7329,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="26"/>
@@ -7412,7 +7412,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="U14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -7685,11 +7685,11 @@
       </c>
       <c r="U15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="26"/>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="U16" s="26"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="26"/>
@@ -7821,7 +7821,7 @@
       <c r="P17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-·</t>
+–</t>
         </is>
       </c>
       <c r="Q17" s="26" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="P18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q18" s="27"/>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -3493,12 +3493,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–姑‹</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–姑‹</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -5934,13 +5934,12 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I140" s="3"/>
@@ -5974,13 +5973,12 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I141" s="2"/>
@@ -6293,13 +6291,12 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I150" s="2"/>
@@ -6689,8 +6686,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C5" s="25"/>
@@ -6797,8 +6793,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-△</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="C6" s="27"/>
@@ -7549,7 +7544,7 @@
       <c r="K14" s="27"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–姑‹</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="M14" s="27" t="inlineStr">
@@ -7594,8 +7589,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-⁚</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C15" s="24"/>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -6491,7 +6491,8 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">가를</t>
+          <t xml:space="preserve">가
+를</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -6502,7 +6503,8 @@
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">임그</t>
+          <t xml:space="preserve">임
+그</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -6513,7 +6515,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">하늘</t>
+          <t xml:space="preserve">하
+늘</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -6524,7 +6527,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">못오</t>
+          <t xml:space="preserve">못
+오</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -6535,7 +6539,8 @@
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">물이</t>
+          <t xml:space="preserve">물
+이</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -6557,7 +6562,8 @@
       </c>
       <c r="Q3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞산</t>
+          <t xml:space="preserve">앞
+산</t>
         </is>
       </c>
       <c r="R3" s="21" t="inlineStr">
@@ -6568,7 +6574,8 @@
       </c>
       <c r="S3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">세월</t>
+          <t xml:space="preserve">세
+월</t>
         </is>
       </c>
       <c r="T3" s="23" t="inlineStr">
@@ -6579,7 +6586,8 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">장을</t>
+          <t xml:space="preserve">장
+을</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6717,8 @@
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">이마</t>
+          <t xml:space="preserve">이
+마</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -6720,7 +6729,8 @@
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">래무</t>
+          <t xml:space="preserve">래
+무</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
@@ -6731,7 +6741,8 @@
       </c>
       <c r="K5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">세월</t>
+          <t xml:space="preserve">세
+월</t>
         </is>
       </c>
       <c r="L5" s="23" t="inlineStr">
@@ -6742,7 +6753,8 @@
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어어</t>
+          <t xml:space="preserve">어
+어</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
@@ -6764,7 +6776,8 @@
       </c>
       <c r="Q5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">까지</t>
+          <t xml:space="preserve">까
+지</t>
         </is>
       </c>
       <c r="R5" s="21" t="inlineStr">
@@ -6775,7 +6788,8 @@
       </c>
       <c r="S5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">라아</t>
+          <t xml:space="preserve">라
+아</t>
         </is>
       </c>
       <c r="T5" s="23" t="inlineStr">
@@ -6825,7 +6839,8 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">엇이</t>
+          <t xml:space="preserve">엇
+이</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -6919,7 +6934,8 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">높다</t>
+          <t xml:space="preserve">높
+다</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -6930,7 +6946,8 @@
       </c>
       <c r="K7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">밉기</t>
+          <t xml:space="preserve">밉
+기</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -6941,7 +6958,8 @@
       </c>
       <c r="M7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">못오</t>
+          <t xml:space="preserve">못
+오</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -6952,7 +6970,8 @@
       </c>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
@@ -6974,7 +6993,8 @@
       </c>
       <c r="S7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">못오</t>
+          <t xml:space="preserve">못
+오</t>
         </is>
       </c>
       <c r="T7" s="23" t="inlineStr">
@@ -7100,7 +7120,8 @@
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">여도</t>
+          <t xml:space="preserve">여
+도</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -7111,7 +7132,9 @@
       </c>
       <c r="K9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">하구나</t>
+          <t xml:space="preserve">하
+구
+나</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -7253,7 +7276,8 @@
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이히</t>
+          <t xml:space="preserve">이
+히</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -7264,7 +7288,8 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">땅아</t>
+          <t xml:space="preserve">땅
+아</t>
         </is>
       </c>
       <c r="J11" s="23"/>
@@ -7277,7 +7302,8 @@
       </c>
       <c r="M11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">해와</t>
+          <t xml:space="preserve">해
+와</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
@@ -7288,7 +7314,8 @@
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">산산</t>
+          <t xml:space="preserve">산
+산</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -7298,7 +7325,8 @@
       </c>
       <c r="Q11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">다시</t>
+          <t xml:space="preserve">다
+시</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
@@ -7320,7 +7348,8 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">가신</t>
+          <t xml:space="preserve">가
+신</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7453,8 @@
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -7435,7 +7465,8 @@
       </c>
       <c r="G13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">히아</t>
+          <t xml:space="preserve">히
+아</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -7459,7 +7490,8 @@
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">은다</t>
+          <t xml:space="preserve">은
+다</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
@@ -7470,7 +7502,8 @@
       </c>
       <c r="O13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">높아</t>
+          <t xml:space="preserve">높
+아</t>
         </is>
       </c>
       <c r="P13" s="23" t="inlineStr">
@@ -7481,7 +7514,8 @@
       </c>
       <c r="Q13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">온다</t>
+          <t xml:space="preserve">온
+다</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
@@ -7537,7 +7571,8 @@
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">엇이</t>
+          <t xml:space="preserve">엇
+이</t>
         </is>
       </c>
       <c r="J14" s="23"/>
@@ -7612,7 +7647,8 @@
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이</t>
+          <t xml:space="preserve">이
+이</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -7623,7 +7659,8 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">깊다</t>
+          <t xml:space="preserve">깊
+다</t>
         </is>
       </c>
       <c r="J15" s="23"/>
@@ -7636,7 +7673,8 @@
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">바뀌</t>
+          <t xml:space="preserve">바
+뀌</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
@@ -7647,7 +7685,8 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">못오</t>
+          <t xml:space="preserve">못
+오</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -7658,7 +7697,8 @@
       </c>
       <c r="Q15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">철하</t>
+          <t xml:space="preserve">철
+하</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
@@ -7669,7 +7709,9 @@
       </c>
       <c r="S15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아아</t>
+          <t xml:space="preserve">아
+아
+아</t>
         </is>
       </c>
       <c r="T15" s="23" t="inlineStr">
@@ -7785,7 +7827,8 @@
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">여도</t>
+          <t xml:space="preserve">여
+도</t>
         </is>
       </c>
       <c r="J17" s="23"/>
@@ -7809,7 +7852,8 @@
       </c>
       <c r="O17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">나아</t>
+          <t xml:space="preserve">나
+아</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +247,27 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6482,14 +6508,14 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南林</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 를</t>
@@ -6501,7 +6527,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">임
 그</t>
@@ -6513,7 +6539,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 늘</t>
@@ -6525,7 +6551,7 @@
 南</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 오</t>
@@ -6537,7 +6563,7 @@
 南</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">물
 이</t>
@@ -6549,7 +6575,7 @@
 –㴌汰</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -6560,7 +6586,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">앞
 산</t>
@@ -6572,7 +6598,7 @@
 汰</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">세
 월</t>
@@ -6584,7 +6610,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="U3" s="24" t="inlineStr">
+      <c r="U3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">장
 을</t>
@@ -6598,13 +6624,13 @@
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -6614,7 +6640,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -6624,7 +6650,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -6634,7 +6660,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6644,7 +6670,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">깊</t>
         </is>
@@ -6654,7 +6680,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
@@ -6664,7 +6690,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="Q4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6674,7 +6700,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S4" s="26" t="inlineStr">
+      <c r="S4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">따</t>
         </is>
@@ -6684,7 +6710,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U4" s="26" t="inlineStr">
+      <c r="U4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -6697,14 +6723,14 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
@@ -6715,7 +6741,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 마</t>
@@ -6727,7 +6753,7 @@
 △㴌</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">래
 무</t>
@@ -6739,7 +6765,7 @@
 △㴌</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">세
 월</t>
@@ -6751,7 +6777,7 @@
 △㴌</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 어</t>
@@ -6763,7 +6789,7 @@
 –</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6774,7 +6800,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">까
 지</t>
@@ -6786,7 +6812,7 @@
 –㴌汰</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라
 아</t>
@@ -6797,7 +6823,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U5" s="26" t="inlineStr">
+      <c r="U5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6810,13 +6836,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -6827,7 +6853,7 @@
 △</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -6837,7 +6863,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">엇
 이</t>
@@ -6848,7 +6874,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="K6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6858,7 +6884,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M6" s="27" t="inlineStr">
+      <c r="M6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -6868,7 +6894,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="O6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
@@ -6878,7 +6904,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="27" t="inlineStr">
+      <c r="Q6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6888,7 +6914,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="27" t="inlineStr">
+      <c r="S6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -6898,7 +6924,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U6" s="27"/>
+      <c r="U6" s="35"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -6908,20 +6934,20 @@
 汰</t>
         </is>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="32"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -6932,7 +6958,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">높
 다</t>
@@ -6944,7 +6970,7 @@
 南</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">밉
 기</t>
@@ -6956,7 +6982,7 @@
 南</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 오</t>
@@ -6968,7 +6994,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="O7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -6980,7 +7006,7 @@
 潢南</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -6991,7 +7017,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="S7" s="24" t="inlineStr">
+      <c r="S7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 오</t>
@@ -7002,7 +7028,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U7" s="24"/>
+      <c r="U7" s="32"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -7011,25 +7037,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -7039,7 +7065,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -7049,7 +7075,7 @@
           <t xml:space="preserve">△林</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -7059,13 +7085,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="34"/>
       <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="Q8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -7075,7 +7101,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="S8" s="26" t="inlineStr">
+      <c r="S8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -7085,7 +7111,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="26"/>
+      <c r="U8" s="34"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -7094,20 +7120,20 @@
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="C9" s="26"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E9" s="26"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -7118,7 +7144,7 @@
 湳</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">여
 도</t>
@@ -7130,7 +7156,7 @@
 南</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 구
@@ -7143,7 +7169,7 @@
 –</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr">
+      <c r="M9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -7154,14 +7180,14 @@
 –</t>
         </is>
       </c>
-      <c r="O9" s="26"/>
+      <c r="O9" s="34"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">덜</t>
         </is>
@@ -7172,7 +7198,7 @@
 –</t>
         </is>
       </c>
-      <c r="S9" s="26" t="inlineStr">
+      <c r="S9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -7182,7 +7208,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U9" s="26"/>
+      <c r="U9" s="34"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -7191,62 +7217,62 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="36"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="30"/>
+      <c r="I10" s="37"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="35"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="35"/>
       <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O10" s="27"/>
+      <c r="O10" s="35"/>
       <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="27"/>
+      <c r="Q10" s="35"/>
       <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S10" s="27"/>
+      <c r="S10" s="35"/>
       <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U10" s="27"/>
+      <c r="U10" s="35"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -7256,14 +7282,14 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 汰</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7274,7 +7300,7 @@
 –</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 히</t>
@@ -7286,21 +7312,21 @@
 南</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">땅
 아</t>
         </is>
       </c>
       <c r="J11" s="23"/>
-      <c r="K11" s="24"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="M11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">해
 와</t>
@@ -7312,7 +7338,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="O11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">산
 산</t>
@@ -7323,7 +7349,7 @@
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 시</t>
@@ -7335,7 +7361,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="S11" s="24" t="inlineStr">
+      <c r="S11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7346,7 +7372,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="U11" s="24" t="inlineStr">
+      <c r="U11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 신</t>
@@ -7360,19 +7386,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="26"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="26"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -7382,19 +7408,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
       <c r="J12" s="23"/>
-      <c r="K12" s="26"/>
+      <c r="K12" s="34"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
@@ -7404,7 +7430,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="26" t="inlineStr">
+      <c r="O12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -7414,13 +7440,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q12" s="26"/>
+      <c r="Q12" s="34"/>
       <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="S12" s="26" t="inlineStr">
+      <c r="S12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7430,7 +7456,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U12" s="26" t="inlineStr">
+      <c r="U12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -7444,14 +7470,14 @@
 南林</t>
         </is>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -7463,7 +7489,7 @@
 南</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">히
 아</t>
@@ -7475,20 +7501,20 @@
 㴌</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J13" s="23"/>
-      <c r="K13" s="26"/>
+      <c r="K13" s="34"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">은
 다</t>
@@ -7500,7 +7526,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O13" s="26" t="inlineStr">
+      <c r="O13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">높
 아</t>
@@ -7512,7 +7538,7 @@
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="26" t="inlineStr">
+      <c r="Q13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">온
 다</t>
@@ -7524,7 +7550,7 @@
 –</t>
         </is>
       </c>
-      <c r="S13" s="26" t="inlineStr">
+      <c r="S13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7534,7 +7560,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U13" s="26" t="inlineStr">
+      <c r="U13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7547,13 +7573,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7563,26 +7589,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">엇
 이</t>
         </is>
       </c>
       <c r="J14" s="23"/>
-      <c r="K14" s="27"/>
+      <c r="K14" s="35"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
+      <c r="M14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -7592,13 +7618,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="35"/>
       <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -7608,7 +7634,7 @@
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="S14" s="27" t="inlineStr">
+      <c r="S14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7618,7 +7644,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U14" s="27"/>
+      <c r="U14" s="35"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -7627,14 +7653,14 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C15" s="24"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
 姑</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7645,7 +7671,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이</t>
@@ -7657,21 +7683,21 @@
 南</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">깊
 다</t>
         </is>
       </c>
       <c r="J15" s="23"/>
-      <c r="K15" s="24"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="M15" s="24" t="inlineStr">
+      <c r="M15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 뀌</t>
@@ -7683,7 +7709,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O15" s="24" t="inlineStr">
+      <c r="O15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 오</t>
@@ -7695,7 +7721,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="inlineStr">
+      <c r="Q15" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">철
 하</t>
@@ -7707,7 +7733,7 @@
 姑</t>
         </is>
       </c>
-      <c r="S15" s="24" t="inlineStr">
+      <c r="S15" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아
@@ -7719,7 +7745,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U15" s="24"/>
+      <c r="U15" s="32"/>
     </row>
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
@@ -7728,37 +7754,37 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="26"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△林</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
       <c r="J16" s="23"/>
-      <c r="K16" s="26"/>
+      <c r="K16" s="34"/>
       <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="M16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -7768,7 +7794,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O16" s="26" t="inlineStr">
+      <c r="O16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -7778,7 +7804,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q16" s="26" t="inlineStr">
+      <c r="Q16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">던</t>
         </is>
@@ -7788,13 +7814,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S16" s="26"/>
+      <c r="S16" s="34"/>
       <c r="T16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U16" s="26"/>
+      <c r="U16" s="34"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -7804,42 +7830,42 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="26"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南林</t>
         </is>
       </c>
-      <c r="E17" s="26"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
 姑</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">여
 도</t>
         </is>
       </c>
       <c r="J17" s="23"/>
-      <c r="K17" s="26"/>
+      <c r="K17" s="34"/>
       <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="M17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -7850,7 +7876,7 @@
 △㴌</t>
         </is>
       </c>
-      <c r="O17" s="26" t="inlineStr">
+      <c r="O17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 아</t>
@@ -7862,7 +7888,7 @@
 –</t>
         </is>
       </c>
-      <c r="Q17" s="26" t="inlineStr">
+      <c r="Q17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -7873,14 +7899,14 @@
 –</t>
         </is>
       </c>
-      <c r="S17" s="26"/>
+      <c r="S17" s="34"/>
       <c r="T17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="U17" s="26" t="inlineStr">
+      <c r="U17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7893,40 +7919,40 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="30"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I18" s="27"/>
+      <c r="I18" s="35"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="27"/>
+      <c r="K18" s="35"/>
       <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="27"/>
+      <c r="M18" s="35"/>
       <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="O18" s="27" t="inlineStr">
+      <c r="O18" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -7936,19 +7962,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q18" s="27"/>
+      <c r="Q18" s="35"/>
       <c r="R18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S18" s="27"/>
+      <c r="S18" s="35"/>
       <c r="T18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢△</t>
         </is>
       </c>
-      <c r="U18" s="27" t="inlineStr">
+      <c r="U18" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -993,10 +993,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -939,17 +939,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -979,7 +979,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -991,9 +991,6 @@
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFF8CBAD"/>
       </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1072,72 +1069,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1150,7 +1159,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1170,14 +1179,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1203,7 +1204,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1364,169 +1365,169 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="76" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="65.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1549,2396 +1550,2396 @@
   <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="A8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="A9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="A10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="A11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="A12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="A13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="A14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="A16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="A17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4" t="n">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="E18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="A19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="E19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="A20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="4" t="n">
+      <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K21" s="4"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="A22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="A24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="F24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="K24" s="4"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="A25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="A26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="A27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="E27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="4" t="n">
+      <c r="A28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="4" t="n">
+      <c r="A29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="4" t="n">
+      <c r="A30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="4" t="n">
+      <c r="A31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="4" t="s">
+      <c r="F31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="4" t="n">
+      <c r="A32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="F32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="4" t="n">
+      <c r="A33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="4" t="n">
+      <c r="A34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="E34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="A35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="E35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="A36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="4" t="n">
+      <c r="A37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="s">
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" s="4" t="n">
+      <c r="A38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="F38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="4" t="n">
+      <c r="A39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="4" t="s">
+      <c r="F39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="A40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="F40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="4" t="n">
+      <c r="A41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="4" t="s">
+      <c r="F41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="4" t="n">
+      <c r="A42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="E42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="A43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="E43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="4" t="n">
+      <c r="A44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="s">
+      <c r="F44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" s="4" t="n">
+      <c r="A45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="A46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="s">
+      <c r="E46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="4" t="n">
+      <c r="A47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="E47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" s="4" t="n">
+      <c r="A48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="s">
+      <c r="F48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" s="4" t="n">
+      <c r="A49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="s">
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="K49" s="4"/>
+      <c r="K49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="4" t="n">
+      <c r="A50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="F50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H50" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="4" t="n">
+      <c r="A51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="F51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I51" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" s="4" t="n">
+      <c r="A52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="4" t="s">
+      <c r="F52" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" s="4" t="n">
+      <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" s="5" t="s">
+      <c r="F53" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I53" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="K53" s="4"/>
+      <c r="K53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="4" t="n">
+      <c r="A54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="E54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="J54" s="3"/>
-      <c r="K54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="4" t="n">
+      <c r="A55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="4" t="s">
+      <c r="E55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="I55" s="4" t="s">
+      <c r="I55" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="4" t="n">
+      <c r="A56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="s">
+      <c r="F56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="4" t="n">
+      <c r="A57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="s">
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="I57" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C58" s="4" t="n">
+      <c r="A58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="4" t="s">
+      <c r="F58" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="I58" s="4" t="s">
+      <c r="I58" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" s="4" t="n">
+      <c r="A59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="F59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="I59" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" s="4" t="n">
+      <c r="A60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="4" t="s">
+      <c r="F60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H60" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I60" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="A61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="F61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H61" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I61" s="4"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="4"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="4" t="n">
+      <c r="A62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4" t="s">
+      <c r="E62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H62" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="A63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="4" t="s">
+      <c r="E63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="H63" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64" s="4" t="n">
+      <c r="A64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="s">
+      <c r="F64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H64" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I64" s="4"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="4"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" s="4" t="n">
+      <c r="A65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="6" t="s">
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="H65" s="6" t="s">
+      <c r="H65" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="I65" s="6"/>
-      <c r="J65" s="3" t="s">
+      <c r="I65" s="7"/>
+      <c r="J65" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="K65" s="6" t="s">
+      <c r="K65" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" s="4" t="n">
+      <c r="A66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="4" t="s">
+      <c r="F66" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H66" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="I66" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="4" t="n">
+      <c r="A67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" s="4" t="s">
+      <c r="F67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="H67" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="I67" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="4" t="n">
+      <c r="A68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" s="4" t="s">
+      <c r="F68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H68" s="4" t="s">
+      <c r="H68" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I68" s="4" t="s">
+      <c r="I68" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="4" t="n">
+      <c r="A69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" s="5" t="s">
+      <c r="F69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="I69" s="5"/>
-      <c r="J69" s="3" t="s">
+      <c r="I69" s="6"/>
+      <c r="J69" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="K69" s="4"/>
+      <c r="K69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="4" t="n">
+      <c r="A70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="5" t="s">
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H70" s="5" t="s">
+      <c r="H70" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="I70" s="5"/>
-      <c r="J70" s="3" t="s">
+      <c r="I70" s="6"/>
+      <c r="J70" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="K70" s="4"/>
+      <c r="K70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" s="4" t="n">
+      <c r="A71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="5" t="s">
+      <c r="E71" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="H71" s="5" t="s">
+      <c r="H71" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="I71" s="5"/>
-      <c r="J71" s="3" t="s">
+      <c r="I71" s="6"/>
+      <c r="J71" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K71" s="4"/>
+      <c r="K71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="4" t="n">
+      <c r="A72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="4" t="s">
+      <c r="F72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="H72" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="I72" s="4"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="4"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="4" t="n">
+      <c r="A73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="4" t="s">
+      <c r="F73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="H73" s="4" t="s">
+      <c r="H73" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="I73" s="4"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="4"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="4" t="n">
+      <c r="A74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" s="4" t="s">
+      <c r="F74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H74" s="4" t="s">
+      <c r="H74" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I74" s="4"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="4"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="4" t="n">
+      <c r="A75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="4" t="s">
+      <c r="F75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H75" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="I75" s="4"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="4"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="4" t="n">
+      <c r="A76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" s="4" t="s">
+      <c r="F76" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="H76" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="4"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="4"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="4" t="n">
+      <c r="A77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="5" t="s">
+      <c r="F77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H77" s="5" t="s">
+      <c r="H77" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I77" s="5"/>
-      <c r="J77" s="3" t="s">
+      <c r="I77" s="6"/>
+      <c r="J77" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="K77" s="4"/>
+      <c r="K77" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K77"/>
@@ -3956,502 +3957,502 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="7" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B3" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="T3" s="10" t="s">
+      <c r="T3" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="17" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B4" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B5" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="R5" s="10" t="s">
+      <c r="R5" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="T5" s="10" t="s">
+      <c r="T5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
+      <c r="U5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B6" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="8" t="s">
+      <c r="O6" s="19"/>
+      <c r="P6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Q6" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="S6" s="14" t="s">
+      <c r="S6" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="U6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="s">
+      <c r="U6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="10" t="s">
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="R7" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="S7" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="T7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="17" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B8" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="10" t="s">
+      <c r="J8" s="16"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="Q8" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="R8" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="T8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="13" t="s">
+      <c r="U8" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B9" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="10" t="s">
+      <c r="J9" s="16"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q9" s="12" t="s">
+      <c r="Q9" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="R9" s="10" t="s">
+      <c r="R9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="T9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U9" s="13"/>
-    </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+      <c r="B10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="19"/>
+      <c r="F10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="19"/>
+      <c r="H10" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="10" t="s">
+      <c r="J10" s="16"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="O10" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="P10" s="10" t="s">
+      <c r="P10" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="Q10" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="R10" s="10" t="s">
+      <c r="R10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="S10" s="14"/>
-      <c r="T10" s="10" t="s">
+      <c r="S10" s="19"/>
+      <c r="T10" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="U10" s="14" t="s">
+      <c r="U10" s="19" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4461,7 +4462,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/님타령.xlsx
+++ b/sheets/민요/검수/님타령.xlsx
@@ -3963,30 +3963,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.56" customHeight="true">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -4010,7 +4010,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B3" s="16" t="s">
         <v>193</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B4" s="16" t="s">
         <v>196</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B5" s="16" t="s">
         <v>186</v>
       </c>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="U5" s="18"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B6" s="16" t="s">
         <v>199</v>
       </c>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="U6" s="19"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B7" s="16" t="s">
         <v>80</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B8" s="16" t="s">
         <v>190</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B9" s="16" t="s">
         <v>201</v>
       </c>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="U9" s="18"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="194.45" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="229.49" customHeight="true">
       <c r="B10" s="16" t="s">
         <v>83</v>
       </c>
@@ -4462,7 +4462,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
